--- a/References/Hybrid SDLC Agile Templates/TGI - DSY - DAVID - Hybrid SDLC Agile.xlsx
+++ b/References/Hybrid SDLC Agile Templates/TGI - DSY - DAVID - Hybrid SDLC Agile.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="148">
   <si>
     <t>Template Name</t>
   </si>
@@ -315,6 +315,12 @@
   </si>
   <si>
     <t>Use the matrix as the cross-department reporting view. Milestone marks the primary owning department and Waiting is the recommended initial state; replace these with current status or target week as planning progresses. Imported Sub-Tasks remain the source of progress percentages.</t>
+  </si>
+  <si>
+    <t>Parallel planning</t>
+  </si>
+  <si>
+    <t>Independent departmental readiness checkpoints run in parallel after the target workflow is approved. LINK HUB business processes also run as parallel workstreams; design/build/QA/UAT/release gates inside each process remain sequential.</t>
   </si>
   <si>
     <t>Task Board</t>
@@ -3918,15 +3924,15 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2" t="s">
-        <v>50</v>
+        <v>102</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2" t="s">
-        <v>103</v>
+        <v>50</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>104</v>
@@ -3949,8 +3955,12 @@
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
+      <c r="A14" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2"/>
@@ -4719,7 +4729,7 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="4" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -4727,30 +4737,30 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -4758,13 +4768,13 @@
         <v>10</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -4772,41 +4782,41 @@
         <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -5987,22 +5997,22 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="F1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -6013,10 +6023,10 @@
         <v>28</v>
       </c>
       <c r="C2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E2" t="s">
         <v>34</v>
@@ -6027,27 +6037,27 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D3" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E3" t="s">
         <v>50</v>
       </c>
       <c r="F3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="B4" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C4" t="s">
         <v>29</v>
@@ -6058,7 +6068,7 @@
     </row>
     <row r="5" spans="1:6">
       <c r="B5" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
   </sheetData>
